--- a/config.xlsx
+++ b/config.xlsx
@@ -8,14 +8,14 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\chris\Dropbox\07 Entwicklungen\01_Vokabel_App\03_Test\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5EA91F3D-FFAB-437F-98CA-C3C6AA280F62}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D25F6ECD-E0CD-4582-9F7B-AD74C6573AB7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3036" yWindow="3036" windowWidth="9756" windowHeight="8880" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Config" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="0" iterateDelta="1E-4"/>
 </workbook>
 </file>
 
@@ -28,10 +28,10 @@
     <t>Dateiname</t>
   </si>
   <si>
-    <t>vocabolario.xlsx</t>
+    <t>VocabolarIo</t>
   </si>
   <si>
-    <t>VocabolarIo A1-A2</t>
+    <t>vocabolario_V2.4.xlsx</t>
   </si>
 </sst>
 </file>
@@ -394,10 +394,10 @@
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B2" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
   </sheetData>
